--- a/tmp/equacao_pre_dimensionamento.xlsx
+++ b/tmp/equacao_pre_dimensionamento.xlsx
@@ -495,22 +495,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2.793360096413218</v>
+        <v>2.987834308316526</v>
       </c>
       <c r="E2" t="n">
-        <v>41.58539580037238</v>
+        <v>43.30032901240965</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2069155626972754</v>
+        <v>0.2213210598752982</v>
       </c>
       <c r="G2" t="n">
         <v>20</v>
       </c>
       <c r="H2" t="n">
-        <v>2.859298400814019</v>
+        <v>3.085616005133334</v>
       </c>
       <c r="I2" t="n">
-        <v>2.360537206981224</v>
+        <v>3.272661289973022</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
@@ -531,22 +531,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2.278249194072044</v>
+        <v>2.463973760303255</v>
       </c>
       <c r="E3" t="n">
-        <v>36.1047448323258</v>
+        <v>37.771035565999</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1687591995608921</v>
+        <v>0.1825165748372782</v>
       </c>
       <c r="G3" t="n">
         <v>30</v>
       </c>
       <c r="H3" t="n">
-        <v>2.337003264749822</v>
+        <v>2.501620516041925</v>
       </c>
       <c r="I3" t="n">
-        <v>2.578913265092121</v>
+        <v>1.527887851128581</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -567,22 +567,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.997740930468128</v>
+        <v>2.154356729234808</v>
       </c>
       <c r="E4" t="n">
-        <v>32.7882327231521</v>
+        <v>34.50082615966561</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1479808096643058</v>
+        <v>0.1595819799433191</v>
       </c>
       <c r="G4" t="n">
         <v>40</v>
       </c>
       <c r="H4" t="n">
-        <v>2.025377657445405</v>
+        <v>2.155611256416356</v>
       </c>
       <c r="I4" t="n">
-        <v>1.383398946068596</v>
+        <v>0.05823210077159334</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -603,22 +603,22 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.817437055535568</v>
+        <v>1.902570534085073</v>
       </c>
       <c r="E5" t="n">
-        <v>30.40981315613967</v>
+        <v>31.80642995897011</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1346249670767087</v>
+        <v>0.1409311506729684</v>
       </c>
       <c r="G5" t="n">
         <v>50</v>
       </c>
       <c r="H5" t="n">
-        <v>1.812575755317742</v>
+        <v>1.920539488649653</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2674810774336804</v>
+        <v>0.9444566833481891</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
@@ -639,22 +639,22 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.664982179631355</v>
+        <v>1.745345866891513</v>
       </c>
       <c r="E6" t="n">
-        <v>28.61320119289024</v>
+        <v>30.1175187685287</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1233320133060263</v>
+        <v>0.129284879029001</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
       </c>
       <c r="H6" t="n">
-        <v>1.655411060438366</v>
+        <v>1.747632023780952</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5748481461290248</v>
+        <v>0.1309858941317533</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
@@ -675,22 +675,22 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4.690470938133339</v>
+        <v>5.089167025173537</v>
       </c>
       <c r="E7" t="n">
-        <v>50.0565129808774</v>
+        <v>52.36706380008528</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2605817187851855</v>
+        <v>0.2827315013985298</v>
       </c>
       <c r="G7" t="n">
         <v>20</v>
       </c>
       <c r="H7" t="n">
-        <v>4.65699404564357</v>
+        <v>5.006799835056714</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7137213497605048</v>
+        <v>-1.618480779062536</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
@@ -711,22 +711,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3.898715426182167</v>
+        <v>4.075739704689213</v>
       </c>
       <c r="E8" t="n">
-        <v>44.05652684264814</v>
+        <v>45.85402521435842</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2165953014545648</v>
+        <v>0.2264299835938452</v>
       </c>
       <c r="G8" t="n">
         <v>30</v>
       </c>
       <c r="H8" t="n">
-        <v>3.806321958383598</v>
+        <v>4.059193744865208</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.369843851082146</v>
+        <v>-0.4059621325907674</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
@@ -747,22 +747,22 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3.366124013626187</v>
+        <v>3.694451453577154</v>
       </c>
       <c r="E9" t="n">
-        <v>40.21016628507971</v>
+        <v>43.05068280090355</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1870068896458993</v>
+        <v>0.2052473029765086</v>
       </c>
       <c r="G9" t="n">
         <v>40</v>
       </c>
       <c r="H9" t="n">
-        <v>3.29877136580691</v>
+        <v>3.497750227220978</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.000896210199954</v>
+        <v>-5.324233619735876</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2.961284512506006</v>
+        <v>3.162802575286086</v>
       </c>
       <c r="E10" t="n">
-        <v>36.98088601252041</v>
+        <v>38.70800876656642</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1645158062503337</v>
+        <v>0.1757112541825603</v>
       </c>
       <c r="G10" t="n">
         <v>50</v>
       </c>
       <c r="H10" t="n">
-        <v>2.952176833795835</v>
+        <v>3.116316735132918</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3075583812263936</v>
+        <v>-1.469767367600037</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
@@ -819,22 +819,22 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2.760082041630822</v>
+        <v>2.844741888799267</v>
       </c>
       <c r="E11" t="n">
-        <v>34.84153929307306</v>
+        <v>36.46761472783696</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1533378912017123</v>
+        <v>0.1580412160444037</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
       </c>
       <c r="H11" t="n">
-        <v>2.696199686384331</v>
+        <v>2.835752638646364</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.314509289323348</v>
+        <v>-0.3159952819725826</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
@@ -855,22 +855,22 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.933241039211455</v>
+        <v>7.330891380711732</v>
       </c>
       <c r="E12" t="n">
-        <v>57.55909872872024</v>
+        <v>60.12895816616369</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3081440461871758</v>
+        <v>0.3258173946982992</v>
       </c>
       <c r="G12" t="n">
         <v>20</v>
       </c>
       <c r="H12" t="n">
-        <v>6.798707584370183</v>
+        <v>7.288165901078943</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.94041219799526</v>
+        <v>-0.5828142501906832</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
@@ -891,22 +891,22 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>5.605060828850484</v>
+        <v>6.00115923478459</v>
       </c>
       <c r="E13" t="n">
-        <v>50.23680961639727</v>
+        <v>52.54924801142197</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2491138146155771</v>
+        <v>0.2667181882126485</v>
       </c>
       <c r="G13" t="n">
         <v>30</v>
       </c>
       <c r="H13" t="n">
-        <v>5.556818349644493</v>
+        <v>5.908779741913617</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.8606950161482061</v>
+        <v>-1.539360801085118</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
@@ -927,22 +927,22 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.82587120227698</v>
+        <v>5.089737398174898</v>
       </c>
       <c r="E14" t="n">
-        <v>45.68550834238653</v>
+        <v>47.78249191992249</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2144831645456436</v>
+        <v>0.2262105510299955</v>
       </c>
       <c r="G14" t="n">
         <v>40</v>
       </c>
       <c r="H14" t="n">
-        <v>4.815849383529819</v>
+        <v>5.091512498269126</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.207668591371297</v>
+        <v>0.0348760644284879</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
@@ -963,22 +963,22 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.261493190313614</v>
+        <v>4.562195032539481</v>
       </c>
       <c r="E15" t="n">
-        <v>42.40177907096175</v>
+        <v>44.4903616706851</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1893996973472717</v>
+        <v>0.2027642236684214</v>
       </c>
       <c r="G15" t="n">
         <v>50</v>
       </c>
       <c r="H15" t="n">
-        <v>4.309858856080198</v>
+        <v>4.536277485456959</v>
       </c>
       <c r="I15" t="n">
-        <v>1.134946452021064</v>
+        <v>-0.5680937990959914</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
@@ -999,22 +999,22 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.989492743182196</v>
+        <v>4.08401858099314</v>
       </c>
       <c r="E16" t="n">
-        <v>40.26963656156759</v>
+        <v>41.78910698341235</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1773107885858754</v>
+        <v>0.1815119369330284</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
       </c>
       <c r="H16" t="n">
-        <v>3.93615990854557</v>
+        <v>4.127873365371507</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.336832476453775</v>
+        <v>1.073814516478099</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
@@ -1035,22 +1035,22 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>9.313027057873045</v>
+        <v>9.978174847141487</v>
       </c>
       <c r="E17" t="n">
-        <v>63.43523565859909</v>
+        <v>66.72204180882061</v>
       </c>
       <c r="F17" t="n">
-        <v>0.344926928069372</v>
+        <v>0.3695620313756106</v>
       </c>
       <c r="G17" t="n">
         <v>20</v>
       </c>
       <c r="H17" t="n">
-        <v>9.261602415284697</v>
+        <v>9.904814664981982</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5521796755102781</v>
+        <v>-0.7352064208467988</v>
       </c>
       <c r="J17" t="b">
         <v>0</v>
@@ -1071,22 +1071,22 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>7.51079224502173</v>
+        <v>7.907328652079627</v>
       </c>
       <c r="E18" t="n">
-        <v>55.75718741284847</v>
+        <v>58.16936864108953</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2781774905563604</v>
+        <v>0.2928640241510973</v>
       </c>
       <c r="G18" t="n">
         <v>30</v>
       </c>
       <c r="H18" t="n">
-        <v>7.56982729580557</v>
+        <v>8.030191550824922</v>
       </c>
       <c r="I18" t="n">
-        <v>0.786002978886406</v>
+        <v>1.553785154901608</v>
       </c>
       <c r="J18" t="b">
         <v>0</v>
@@ -1107,22 +1107,22 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>6.439473971248886</v>
+        <v>6.770859590773329</v>
       </c>
       <c r="E19" t="n">
-        <v>50.71096070558761</v>
+        <v>52.89201311789211</v>
       </c>
       <c r="F19" t="n">
-        <v>0.238499035972181</v>
+        <v>0.2507725774360492</v>
       </c>
       <c r="G19" t="n">
         <v>40</v>
       </c>
       <c r="H19" t="n">
-        <v>6.560435454627509</v>
+        <v>6.919503252845731</v>
       </c>
       <c r="I19" t="n">
-        <v>1.878437336942341</v>
+        <v>2.195344033938605</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
@@ -1143,22 +1143,22 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>5.734245309541487</v>
+        <v>6.015365616621969</v>
       </c>
       <c r="E20" t="n">
-        <v>47.29756891491404</v>
+        <v>49.24175979582745</v>
       </c>
       <c r="F20" t="n">
-        <v>0.212379455908944</v>
+        <v>0.222791319134147</v>
       </c>
       <c r="G20" t="n">
         <v>50</v>
       </c>
       <c r="H20" t="n">
-        <v>5.871145169233846</v>
+        <v>6.164923846715684</v>
       </c>
       <c r="I20" t="n">
-        <v>2.387408495841021</v>
+        <v>2.486269989648651</v>
       </c>
       <c r="J20" t="b">
         <v>0</v>
@@ -1179,22 +1179,22 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5.299371811680241</v>
+        <v>5.631677718249779</v>
       </c>
       <c r="E21" t="n">
-        <v>45.46294694412061</v>
+        <v>47.59972549193003</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1962730300622312</v>
+        <v>0.2085806562314733</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
       </c>
       <c r="H21" t="n">
-        <v>5.362070314619888</v>
+        <v>5.609891596796318</v>
       </c>
       <c r="I21" t="n">
-        <v>1.183130853386337</v>
+        <v>-0.3868495773978875</v>
       </c>
       <c r="J21" t="b">
         <v>0</v>
